--- a/TFG_Proto1/docs/excel/Comparison Table (SOA).xlsx
+++ b/TFG_Proto1/docs/excel/Comparison Table (SOA).xlsx
@@ -586,12 +586,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>Pattern Recognition journal page lists Impact Factor 7.6</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>Author h-index not found from open metadata</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>N/A (conference/preprint)</t>
+          <t>No official JIF (MICCAI / LNCS conference proceedings)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Olaf Ronneberger=52</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal venue not explicitly fixed in extracted markdown)</t>
+          <t>IEEE Communications Surveys &amp; Tutorials journal (official JIF not exposed on fetched page)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Yong Zeng=67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>N/A (preprint/dataset paper)</t>
+          <t>No official JIF (preprint / arXiv)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Fabian Jaensch=3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>N/A (preprint/dataset paper)</t>
+          <t>No official JIF (preprint / arXiv)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Zijian Wu=33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N/A (preprint/dataset paper)</t>
+          <t>No official JIF (preprint / arXiv)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Xiucheng Wang=17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>Journal/venue matched: INTERNATIONAL JOURNAL OF APPLIED RESEARCH AND TECHNOLOGY (official JIF to verify in JCR)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>Author h-index not found from open metadata</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>Electronics Letters journal (official JIF not exposed on fetched page)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Changpeng Zhou=9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>IEEE Transactions on Wireless Communications journal (official JIF not exposed on fetched page)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Xiaoli Xu=30</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>N/A (conference paper)</t>
+          <t>No official JIF (CVPR conference paper)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Phillip Isola=46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No JIF (internal document / thesis material)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Author h-index not found from open metadata</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>Sensors journal page lists Impact Factor 3.5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Lamia Alhoraibi=5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>N/A (journal metric lookup required)</t>
+          <t>Sensors journal page lists Impact Factor 3.5</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: G.-G. Ge=142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>N/A (conference/proceedings)</t>
+          <t>No official JIF (ACM conference/proceedings paper)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>N/A (author-level metric lookup required)</t>
+          <t>OpenAlex h-index: Joseph Boulis=1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No JIF (internal document / thesis material)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Author h-index not found from open metadata</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Official JIF not reliably verified from open sources (check JCR)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Author h-index not found from open metadata</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
